--- a/Backend/output.xlsx
+++ b/Backend/output.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AE18"/>
+  <dimension ref="A1:AE19"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -908,25 +908,85 @@
     </row>
     <row r="13">
       <c r="B13" t="str">
-        <v xml:space="preserve">avengers </v>
+        <v>Innovators Club</v>
       </c>
       <c r="C13" t="str">
-        <v>mmmut</v>
+        <v>IIT Delhi</v>
       </c>
       <c r="D13" t="str">
-        <v>aman jais</v>
+        <v>Raj Kumar</v>
       </c>
       <c r="E13" t="str">
-        <v>amanj952987@gmail.com</v>
+        <v>rajkumar@example.com</v>
       </c>
       <c r="F13" t="str">
-        <v>9555951834</v>
+        <v>9876543210</v>
       </c>
       <c r="G13" t="str">
-        <v>ECE(IoT)</v>
+        <v>Computer Science</v>
       </c>
       <c r="H13" t="str">
-        <v>3rd</v>
+        <v>3rd Year</v>
+      </c>
+      <c r="I13" t="str">
+        <v>Ankit Sharma</v>
+      </c>
+      <c r="J13" t="str">
+        <v>ankit@example.com</v>
+      </c>
+      <c r="K13" t="str">
+        <v>9123456780</v>
+      </c>
+      <c r="L13" t="str">
+        <v>Mechanical</v>
+      </c>
+      <c r="M13" t="str">
+        <v>2nd Year</v>
+      </c>
+      <c r="N13" t="str">
+        <v>Priya Singh</v>
+      </c>
+      <c r="O13" t="str">
+        <v>priya@example.com</v>
+      </c>
+      <c r="P13" t="str">
+        <v>9988776655</v>
+      </c>
+      <c r="Q13" t="str">
+        <v>Electronics</v>
+      </c>
+      <c r="R13" t="str">
+        <v>3rd Year</v>
+      </c>
+      <c r="S13" t="str">
+        <v>Rohit Verma</v>
+      </c>
+      <c r="T13" t="str">
+        <v>rohit@example.com</v>
+      </c>
+      <c r="U13" t="str">
+        <v>9090909090</v>
+      </c>
+      <c r="V13" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="W13" t="str">
+        <v>4th Year</v>
+      </c>
+      <c r="X13" t="str">
+        <v>Sneha Kapoor</v>
+      </c>
+      <c r="Y13" t="str">
+        <v>sneha@example.com</v>
+      </c>
+      <c r="Z13" t="str">
+        <v>8800554433</v>
+      </c>
+      <c r="AA13" t="str">
+        <v>IT</v>
+      </c>
+      <c r="AB13" t="str">
+        <v>2nd Year</v>
       </c>
       <c r="AC13" t="str">
         <v>https://res.cloudinary.com/dlczp2anq/image/upload/v1755634041/uploadnew/hhfxdqam3aflc8gijsci.png</v>
@@ -940,7 +1000,7 @@
     </row>
     <row r="14">
       <c r="B14" t="str">
-        <v>wow bro</v>
+        <v>Ninjas</v>
       </c>
       <c r="C14" t="str">
         <v>IIT bombay</v>
@@ -961,19 +1021,34 @@
         <v>3rd</v>
       </c>
       <c r="I14" t="str">
-        <v>suraj yadav</v>
+        <v>anup Verma</v>
       </c>
       <c r="J14" t="str">
-        <v>amanjais102@gmail.com</v>
+        <v>ankitverma@example.com</v>
       </c>
       <c r="K14" t="str">
-        <v>9525361456</v>
+        <v>9876543210</v>
       </c>
       <c r="L14" t="str">
-        <v>ECE(IoT)</v>
+        <v>Mechanical</v>
       </c>
       <c r="M14" t="str">
-        <v>3rd</v>
+        <v>2nd Year</v>
+      </c>
+      <c r="S14" t="str">
+        <v>aman Gupta</v>
+      </c>
+      <c r="T14" t="str">
+        <v>sneha.g@example.com</v>
+      </c>
+      <c r="U14" t="str">
+        <v>9123456789</v>
+      </c>
+      <c r="V14" t="str">
+        <v>Civil</v>
+      </c>
+      <c r="W14" t="str">
+        <v>4th Year</v>
       </c>
       <c r="AC14" t="str">
         <v>https://res.cloudinary.com/dlczp2anq/image/upload/v1755686850/uploadnew/rewvxcxthn5nfwuemuuh.jpg</v>
@@ -1173,9 +1248,41 @@
         <v>0</v>
       </c>
     </row>
+    <row r="19">
+      <c r="B19" t="str">
+        <v>faltu log</v>
+      </c>
+      <c r="C19" t="str">
+        <v>mmmut</v>
+      </c>
+      <c r="D19" t="str">
+        <v>Rajneesh Yadav</v>
+      </c>
+      <c r="E19" t="str">
+        <v>rajneeshyadav0507@gmail.com</v>
+      </c>
+      <c r="F19" t="str">
+        <v>09026975515</v>
+      </c>
+      <c r="G19" t="str">
+        <v>ECE</v>
+      </c>
+      <c r="H19" t="str">
+        <v>3rd</v>
+      </c>
+      <c r="AC19" t="str">
+        <v>https://res.cloudinary.com/dlczp2anq/image/upload/v1755851925/uploadnew/bgf1bta6jjh5t8vef8al.jpg</v>
+      </c>
+      <c r="AD19" t="str">
+        <v>1234567890</v>
+      </c>
+      <c r="AE19">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AE18"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AE19"/>
   </ignoredErrors>
 </worksheet>
 </file>